--- a/國軍軍購案執行中個案管制表(範例) - 複製.xlsx
+++ b/國軍軍購案執行中個案管制表(範例) - 複製.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gyzhu\Desktop\電腦小組\1150615研析試作區\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB31ABB-85CA-4836-A4B0-C8D60AB3CFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4D7AE7-322F-43EB-8C5C-E577EB4E7683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3D9305F-6A72-4EB0-884D-54554B853FCB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
   <si>
     <t>項次</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -90,10 +90,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>FRB餘額</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TWBBAA</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -247,8 +243,61 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>累計結匯
+    <t>待平衡支付值
+美元</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>單位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>累計結匯率
 (C)=(B)/(A)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陸軍主計處</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陸勤部</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>海軍主計處</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>海軍保指部</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空軍主計處</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>整評司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TWBZEA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中央、陸軍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陸軍主計處、國防部憲兵指揮部本部</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>獵鳥專案</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FRB</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -294,7 +343,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -317,6 +366,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -326,7 +386,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -339,13 +399,22 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -663,16 +732,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5C7165C-5FEB-433E-8E37-8D06574C010F}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="8" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="15.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="66" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -683,680 +753,822 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="6">
+      <c r="G2" s="5">
         <v>150104</v>
       </c>
-      <c r="G2" s="4">
+      <c r="H2" s="7">
         <v>44263196</v>
       </c>
-      <c r="H2" s="4">
+      <c r="I2" s="7">
         <v>44263196</v>
       </c>
-      <c r="I2" s="5">
-        <f>H2/G2</f>
+      <c r="J2" s="4">
+        <f>I2/H2</f>
         <v>1</v>
       </c>
-      <c r="J2" s="4">
+      <c r="K2" s="7">
         <v>43920244</v>
       </c>
-      <c r="K2" s="5">
-        <f>J2/H2</f>
+      <c r="L2" s="4">
+        <f>K2/I2</f>
         <v>0.99225198288889938</v>
       </c>
-      <c r="L2" s="4">
+      <c r="M2" s="7">
         <v>342951.2</v>
       </c>
-      <c r="M2" s="3">
+      <c r="N2" s="3">
         <v>10106773</v>
       </c>
-      <c r="N2" s="4">
+      <c r="O2" s="7">
+        <v>0</v>
+      </c>
+      <c r="P2" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5">
         <v>150101</v>
       </c>
-      <c r="G3" s="4">
+      <c r="H3" s="7">
         <v>48000000</v>
       </c>
-      <c r="H3" s="4">
+      <c r="I3" s="7">
         <v>41672691</v>
       </c>
-      <c r="I3" s="5">
-        <f t="shared" ref="I3:I15" si="0">H3/G3</f>
+      <c r="J3" s="4">
+        <f t="shared" ref="J3:J16" si="0">I3/H3</f>
         <v>0.86818106250000004</v>
       </c>
-      <c r="J3" s="4">
+      <c r="K3" s="7">
         <v>40316756.359999999</v>
       </c>
-      <c r="K3" s="5">
-        <f t="shared" ref="K3:K15" si="1">J3/H3</f>
+      <c r="L3" s="4">
+        <f t="shared" ref="L3:L16" si="1">K3/I3</f>
         <v>0.96746227307470978</v>
       </c>
-      <c r="L3" s="4">
+      <c r="M3" s="7">
         <v>1355934.64</v>
       </c>
-      <c r="M3" s="3">
+      <c r="N3" s="3">
         <v>44210248</v>
       </c>
-      <c r="N3" s="4">
+      <c r="O3" s="7">
+        <v>0</v>
+      </c>
+      <c r="P3" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="F4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="5">
         <v>150104</v>
       </c>
-      <c r="G4" s="4">
+      <c r="H4" s="7">
         <v>45841795</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="7">
         <v>45841795</v>
       </c>
-      <c r="I4" s="5">
+      <c r="J4" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J4" s="4">
+      <c r="K4" s="7">
         <v>45511302.619999997</v>
       </c>
-      <c r="K4" s="5">
+      <c r="L4" s="4">
         <f t="shared" si="1"/>
         <v>0.9927905881521436</v>
       </c>
-      <c r="L4" s="4">
+      <c r="M4" s="7">
         <v>330492.38</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <v>9658640</v>
       </c>
-      <c r="N4" s="4">
+      <c r="O4" s="7">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="6">
+      <c r="G5" s="5">
         <v>140118</v>
       </c>
-      <c r="G5" s="4">
+      <c r="H5" s="7">
         <v>15303032</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" s="7">
         <v>12382319.84</v>
       </c>
-      <c r="I5" s="5">
+      <c r="J5" s="4">
         <f t="shared" si="0"/>
         <v>0.80914160278825786</v>
       </c>
-      <c r="J5" s="4">
+      <c r="K5" s="7">
         <v>6145939.4299999997</v>
       </c>
-      <c r="K5" s="5">
+      <c r="L5" s="4">
         <f t="shared" si="1"/>
         <v>0.49634797916833651</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="7">
         <v>6236380.4100000001</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>186264134</v>
       </c>
-      <c r="N5" s="4">
+      <c r="O5" s="7">
         <v>1678863.59</v>
       </c>
+      <c r="P5" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="5">
         <v>150104</v>
       </c>
-      <c r="G6" s="4">
+      <c r="H6" s="7">
         <v>377464571</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="7">
         <v>303913064.00999999</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="4">
         <f t="shared" si="0"/>
         <v>0.80514328326194085</v>
       </c>
-      <c r="J6" s="4">
+      <c r="K6" s="7">
         <v>49050287.280000001</v>
       </c>
-      <c r="K6" s="5">
+      <c r="L6" s="4">
         <f t="shared" si="1"/>
         <v>0.1613957841522273</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="7">
         <v>254862776.72999999</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>7582640818</v>
       </c>
-      <c r="N6" s="4">
+      <c r="O6" s="7">
         <v>56728761.810000002</v>
       </c>
+      <c r="P6" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="F7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="5">
         <v>150104</v>
       </c>
-      <c r="G7" s="4">
+      <c r="H7" s="7">
         <v>1416618990</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="7">
         <v>1290295745.0699999</v>
       </c>
-      <c r="I7" s="5">
+      <c r="J7" s="4">
         <f t="shared" si="0"/>
         <v>0.91082764962087648</v>
       </c>
-      <c r="J7" s="4">
+      <c r="K7" s="7">
         <v>342085215.30000001</v>
       </c>
-      <c r="K7" s="5">
+      <c r="L7" s="4">
         <f t="shared" si="1"/>
         <v>0.2651215557418129</v>
       </c>
-      <c r="L7" s="4">
+      <c r="M7" s="7">
         <v>948210529.76999998</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>29116308640</v>
       </c>
-      <c r="N7" s="4">
+      <c r="O7" s="7">
         <v>323362244.93000001</v>
       </c>
+      <c r="P7" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="F8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="5">
         <v>140118</v>
       </c>
-      <c r="G8" s="4">
+      <c r="H8" s="7">
         <v>1258775</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="7">
         <v>911036.74</v>
       </c>
-      <c r="I8" s="5">
+      <c r="J8" s="4">
         <f t="shared" si="0"/>
         <v>0.72374867629242712</v>
       </c>
-      <c r="J8" s="4">
+      <c r="K8" s="7">
         <v>673763.98</v>
       </c>
-      <c r="K8" s="5">
+      <c r="L8" s="4">
         <f t="shared" si="1"/>
         <v>0.73955741894668259</v>
       </c>
-      <c r="L8" s="4">
+      <c r="M8" s="7">
         <v>237272.76</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7134791</v>
       </c>
-      <c r="N8" s="4">
+      <c r="O8" s="7">
         <v>28427.78</v>
       </c>
+      <c r="P8" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>156</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="F9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="5">
         <v>150104</v>
       </c>
-      <c r="G9" s="4">
+      <c r="H9" s="7">
         <v>99396987</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="7">
         <v>39039906.719999999</v>
       </c>
-      <c r="I9" s="5">
+      <c r="J9" s="4">
         <f t="shared" si="0"/>
         <v>0.39276750632290292</v>
       </c>
-      <c r="J9" s="4">
+      <c r="K9" s="7">
         <v>10632183.779999999</v>
       </c>
-      <c r="K9" s="5">
+      <c r="L9" s="4">
         <f t="shared" si="1"/>
         <v>0.27234142377069698</v>
       </c>
-      <c r="L9" s="4">
+      <c r="M9" s="7">
         <v>28407721.940000001</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>897791973</v>
       </c>
-      <c r="N9" s="4">
+      <c r="O9" s="7">
         <v>23724199.530000001</v>
       </c>
+      <c r="P9" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>160</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="F10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="5">
         <v>120115</v>
       </c>
-      <c r="G10" s="4">
+      <c r="H10" s="7">
         <v>634457</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="7">
         <v>634457</v>
       </c>
-      <c r="I10" s="5">
-        <v>0</v>
-      </c>
       <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7">
         <v>59603.68</v>
       </c>
-      <c r="K10" s="5">
+      <c r="L10" s="4">
         <f t="shared" si="1"/>
         <v>9.3944396546968512E-2</v>
       </c>
-      <c r="L10" s="4">
+      <c r="M10" s="7">
         <v>574853.31999999995</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>17177310</v>
       </c>
-      <c r="N10" s="4">
+      <c r="O10" s="7">
         <v>14457</v>
       </c>
+      <c r="P10" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>177</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="F11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="5">
         <v>140118</v>
       </c>
-      <c r="G11" s="4">
+      <c r="H11" s="7">
         <v>49000000</v>
       </c>
-      <c r="H11" s="4">
+      <c r="I11" s="7">
         <v>2000000</v>
       </c>
-      <c r="I11" s="5">
+      <c r="J11" s="4">
         <f t="shared" si="0"/>
         <v>4.0816326530612242E-2</v>
       </c>
-      <c r="J11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5">
+      <c r="K11" s="7">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L11" s="4">
+      <c r="M11" s="7">
         <v>2000000</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>62302000</v>
       </c>
-      <c r="N11" s="4">
+      <c r="O11" s="7">
         <v>2000000</v>
       </c>
+      <c r="P11" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>232</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="F12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="5">
         <v>150104</v>
       </c>
-      <c r="G12" s="4">
+      <c r="H12" s="7">
         <v>882562000</v>
       </c>
-      <c r="H12" s="4">
+      <c r="I12" s="7">
         <v>357068931.48000002</v>
       </c>
-      <c r="I12" s="5">
+      <c r="J12" s="4">
         <f t="shared" si="0"/>
         <v>0.40458226331974412</v>
       </c>
-      <c r="J12" s="4">
+      <c r="K12" s="7">
         <v>5557158.9000000004</v>
       </c>
-      <c r="K12" s="5">
+      <c r="L12" s="4">
         <f t="shared" si="1"/>
         <v>1.5563266389395364E-2</v>
       </c>
-      <c r="L12" s="4">
+      <c r="M12" s="7">
         <v>351511772.57999998</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10348496552</v>
       </c>
-      <c r="N12" s="4">
+      <c r="O12" s="7">
         <v>127507317.2</v>
       </c>
+      <c r="P12" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>237</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="6">
+        <v>38</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="5">
         <v>120115</v>
       </c>
-      <c r="G13" s="4">
+      <c r="H13" s="7">
         <v>238434232</v>
       </c>
-      <c r="H13" s="4">
+      <c r="I13" s="7">
         <v>238434232</v>
       </c>
-      <c r="I13" s="5">
+      <c r="J13" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J13" s="4">
+      <c r="K13" s="7">
         <v>237693847.65000001</v>
       </c>
-      <c r="K13" s="5">
+      <c r="L13" s="4">
         <f t="shared" si="1"/>
         <v>0.99689480682455034</v>
       </c>
-      <c r="L13" s="4">
+      <c r="M13" s="7">
         <v>740384.35</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <v>22185617</v>
       </c>
-      <c r="N13" s="4">
+      <c r="O13" s="7">
+        <v>0</v>
+      </c>
+      <c r="P13" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>244</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="G14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="4">
+      <c r="H14" s="7">
         <v>4900815982</v>
       </c>
-      <c r="H14" s="4">
+      <c r="I14" s="7">
         <v>4900815918.8000002</v>
       </c>
-      <c r="I14" s="5">
+      <c r="J14" s="4">
         <f t="shared" si="0"/>
         <v>0.99999998710418836</v>
       </c>
-      <c r="J14" s="4">
+      <c r="K14" s="7">
         <v>4834734118.7700005</v>
       </c>
-      <c r="K14" s="5">
+      <c r="L14" s="4">
         <f t="shared" si="1"/>
         <v>0.98651616360930772</v>
       </c>
-      <c r="L14" s="4">
+      <c r="M14" s="7">
         <v>66081863.030000001</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2092083645</v>
       </c>
-      <c r="N14" s="4">
+      <c r="O14" s="7">
+        <v>0</v>
+      </c>
+      <c r="P14" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>429</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="F15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="4">
+      <c r="H15" s="7">
         <v>526238</v>
       </c>
-      <c r="H15" s="4">
+      <c r="I15" s="7">
         <v>98023</v>
       </c>
-      <c r="I15" s="5">
+      <c r="J15" s="4">
         <f t="shared" si="0"/>
         <v>0.18627123088792524</v>
       </c>
-      <c r="J15" s="4">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5">
+      <c r="K15" s="7">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L15" s="4">
+      <c r="M15" s="7">
         <v>98023</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3019765</v>
       </c>
-      <c r="N15" s="4">
+      <c r="O15" s="7">
         <v>98023</v>
+      </c>
+      <c r="P15" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>446</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="5">
+        <v>450111</v>
+      </c>
+      <c r="H16" s="6">
+        <v>56842784</v>
+      </c>
+      <c r="I16" s="6">
+        <v>31223812.82</v>
+      </c>
+      <c r="J16" s="4">
+        <f t="shared" si="0"/>
+        <v>0.54930125906570659</v>
+      </c>
+      <c r="K16" s="6">
+        <v>56483.63</v>
+      </c>
+      <c r="L16" s="4">
+        <f t="shared" si="1"/>
+        <v>1.8089920768363098E-3</v>
+      </c>
+      <c r="M16" s="6">
+        <v>31167329.190000001</v>
+      </c>
+      <c r="N16" s="9">
+        <v>957072149</v>
+      </c>
+      <c r="O16" s="6">
+        <v>31223812.82</v>
+      </c>
+      <c r="P16" s="6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
